--- a/data/demo_data.xlsx
+++ b/data/demo_data.xlsx
@@ -12,16 +12,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史沿革" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史沿革.股权结构" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史沿革.公司设立" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目基本情况" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPC合同" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPC合同.epc金额" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMC合同" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="购售电合同" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="电量情况" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="电量情况.电量表" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运维合同" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目建设情况.固定资产" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目建设情况" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工厂建设项目" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基建合同" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基建合同.合同分项明细" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售合同" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采购合同" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产销情况" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产销情况.月度产销" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="维保合同" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目建设情况" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目建设情况.固定资产" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目建设情况.使用权资产" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="税率政策" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产负债表" sheetId="18" state="visible" r:id="rId18"/>
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>阳光新能源科技有限公司</t>
+          <t>东海精密制造有限公司</t>
         </is>
       </c>
     </row>
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>阳光新能源</t>
+          <t>东海精密</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>电力公司</t>
+          <t>供应商</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -572,66 +572,66 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>上网模式</t>
+          <t>采购模式</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>电费计算</t>
+          <t>定价方式</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>国网浙江省电力有限公司杭州供电公司</t>
+          <t>东方钢铁贸易有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州钱塘区6.923MW分布式光伏购售电合同</t>
+          <t>金属原材料年度采购合同</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>自发自用，余电上网</t>
+          <t>年度框架+月度订单</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>余电上网按标杆电价0.4153元/kWh</t>
+          <t>参考市场价月度定价</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>国网浙江省电力有限公司宁波供电公司</t>
+          <t>南方材料批发有限公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>宁波北仑3.5MW全额上网购售电合同</t>
+          <t>零件毛坯采购合同</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全额上网</t>
+          <t>批次采购</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>按标杆电价0.4153元/kWh结算</t>
+          <t>招标定价</t>
         </is>
       </c>
     </row>
@@ -657,12 +657,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>开始发电月</t>
+          <t>开始生产月</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>并网月</t>
+          <t>投产月</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>上网单价</t>
+          <t>外销单价</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -692,14 +692,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>未结算上网月份</t>
+          <t>未结算外销月份</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -713,30 +713,30 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.72</v>
+        <v>0.3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4153</v>
+        <v>8500</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>7500</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>按月结算，次月支付</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>2026年4月</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4153</v>
+        <v>9200</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -797,17 +797,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>自用电量</t>
+          <t>自用量</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>上网电量</t>
+          <t>外销量</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>合计电量</t>
+          <t>合计产量</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -828,22 +828,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>420000</v>
+        <v>150</v>
       </c>
       <c r="D2" t="n">
-        <v>158000</v>
+        <v>350</v>
       </c>
       <c r="E2" t="n">
-        <v>578000</v>
+        <v>500</v>
       </c>
       <c r="F2" t="n">
-        <v>0.727</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -852,22 +852,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>380000</v>
+        <v>140</v>
       </c>
       <c r="D3" t="n">
-        <v>145000</v>
+        <v>330</v>
       </c>
       <c r="E3" t="n">
-        <v>525000</v>
+        <v>470</v>
       </c>
       <c r="F3" t="n">
-        <v>0.724</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>500000</v>
+        <v>165</v>
       </c>
       <c r="D4" t="n">
-        <v>192000</v>
+        <v>385</v>
       </c>
       <c r="E4" t="n">
-        <v>692000</v>
+        <v>550</v>
       </c>
       <c r="F4" t="n">
-        <v>0.723</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -900,22 +900,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>460000</v>
+        <v>160</v>
       </c>
       <c r="D5" t="n">
-        <v>180000</v>
+        <v>370</v>
       </c>
       <c r="E5" t="n">
-        <v>640000</v>
+        <v>530</v>
       </c>
       <c r="F5" t="n">
-        <v>0.719</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -927,10 +927,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>380000</v>
+        <v>280</v>
       </c>
       <c r="E6" t="n">
-        <v>380000</v>
+        <v>280</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -951,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>350000</v>
+        <v>260</v>
       </c>
       <c r="E7" t="n">
-        <v>350000</v>
+        <v>260</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -963,7 +963,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>410000</v>
+        <v>300</v>
       </c>
       <c r="E8" t="n">
-        <v>410000</v>
+        <v>300</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -999,10 +999,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>395000</v>
+        <v>290</v>
       </c>
       <c r="E9" t="n">
-        <v>395000</v>
+        <v>290</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1052,17 +1052,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>5000000</v>
+        <v>3000000</v>
       </c>
       <c r="D2" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="E2" t="n">
         <v>0.06</v>
@@ -1071,17 +1071,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="D3" t="n">
-        <v>120000</v>
+        <v>250000</v>
       </c>
       <c r="E3" t="n">
         <v>0.06</v>
@@ -1098,102 +1098,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>_parent_项目名称</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
           <t>项目名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>原值</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>残值率</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>折旧年限</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>转固时点</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>年折旧额</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>杭州钱塘光伏项目</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>28500000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1353750</v>
+          <t>A区精密加工中心</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>宁波北仑光伏项目</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2022-03-01</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>665000</v>
+          <t>D区自动化装配线</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1207,28 +1133,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>_parent_项目名称</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>项目名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>原值</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>残值率</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>折旧年限</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>转固时点</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>年折旧额</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
-        </is>
+          <t>A区精密加工中心</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A区精密加工中心</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1353750</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
-        </is>
+          <t>D区自动化装配线</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>D区自动化装配线</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>665000</v>
       </c>
     </row>
   </sheetData>
@@ -1285,12 +1285,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1314,12 +1314,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1419,7 +1419,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>有三免三减半</t>
+          <t>有高新优惠</t>
         </is>
       </c>
       <c r="B7" t="b">
@@ -1439,7 +1439,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>有流转税减免</t>
+          <t>有地方优惠</t>
         </is>
       </c>
       <c r="B9" t="b">
@@ -2427,48 +2427,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>阳光新能源科技有限公司</t>
+          <t>东海精密制造有限公司</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>阳光新能源</t>
+          <t>东海精密</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>光伏发电</t>
+          <t>南山控股集团有限公司</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>南山控股</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>合同能源管理</t>
+          <t>尽调基准日</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EMC</t>
+          <t>2026年4月30日</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>工程总承包</t>
+          <t>高新技术企业</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EPC</t>
+          <t>高新企业</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>杭州阳光控股集团有限公司</t>
+          <t>南山控股集团有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>杭州阳光建设有限公司</t>
+          <t>南山建设工程有限公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EPC工程款</t>
+          <t>基建工程款</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>屋顶出租方情况</t>
+          <t>场地出租方情况</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>屋顶出租方杭州钱塘产业园管理有限公司信用良好。</t>
+          <t>场地出租方B市工业园区管理有限公司信用良好，租赁合同正常履行。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>阳光新能源科技有限公司</t>
+          <t>东海精密制造有限公司</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区江东大道100号</t>
+          <t>A省B市C区工业大道100号</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>张明远</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>有限责任公司（非自然人投资或控股的法人独资）</t>
+          <t>有限责任公司（法人独资）</t>
         </is>
       </c>
     </row>
@@ -2821,8 +2821,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>太阳能发电技术服务；合同能源管理；光伏设备及元器件销售。
-一般项目：技术服务、技术开发、技术咨询。</t>
+          <t>精密机械零部件制造；自动化设备研发与生产；金属材料加工。
+一般项目：技术进出口、货物进出口。</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>杭州阳光控股集团有限公司</t>
+          <t>南山控股集团有限公司</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>杭州市市场监督管理局钱塘新区分局</t>
+          <t>B市市场监督管理局</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>杭州阳光控股集团有限公司</t>
+          <t>南山控股集团有限公司</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2990,7 +2990,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>杭州阳光控股集团有限公司</t>
+          <t>南山控股集团有限公司</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -3017,7 +3017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3033,22 +3033,22 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>装机容量</t>
+          <t>规划产能</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>项目模式</t>
+          <t>运营模式</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>含税总价</t>
+          <t>总投资</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>含税单价</t>
+          <t>建设单价</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -3058,69 +3058,39 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>接入电网审批</t>
+          <t>环境审批</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>环评文件</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>房屋鉴定</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>安全设计审查</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>安全预评价</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>消防备案</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>购售电合同</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>并网验收</t>
+          <t>安全审查</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>杭州市钱塘区</t>
+          <t>A省B市C区</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.923</v>
+        <v>5000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>自发自用，余电上网</t>
+          <t>自产自销</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>28500000</v>
       </c>
       <c r="F2" t="n">
-        <v>4.12</v>
+        <v>5700</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3134,64 +3104,34 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>已备案</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
           <t>已通过</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>已备案</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>已签订</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>宁波市北仑区</t>
+          <t>B市D区</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.5</v>
+        <v>3000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全额上网</t>
+          <t>来料加工</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>14000000</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>4667</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3205,37 +3145,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>已备案</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
           <t>已通过</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>已备案</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>已签订</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>已完成</t>
         </is>
       </c>
     </row>
@@ -3283,22 +3193,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>杭州阳光建设有限公司</t>
+          <t>南山建设工程有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.923MW分布式光伏发电项目EPC总承包</t>
+          <t>精密加工中心厂房及配套设施建设</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>设计、采购、施工总承包</t>
+          <t>设计、土建、安装总承包</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -3308,22 +3218,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>浙江电建有限公司</t>
+          <t>东方建筑安装有限公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.5MW分布式光伏发电项目EPC总承包</t>
+          <t>自动化装配线车间及仓库建设</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>设计、采购、施工总承包</t>
+          <t>设计、土建、设备安装总承包</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -3374,7 +3284,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -3382,11 +3292,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>组件及支架</t>
+          <t>土建工程</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="E2" t="n">
         <v>15000000</v>
@@ -3395,7 +3305,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -3403,20 +3313,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>逆变器及电气</t>
+          <t>设备采购</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>6000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -3424,20 +3334,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>施工安装</t>
+          <t>安装调试</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="E4" t="n">
-        <v>7500000</v>
+        <v>5500000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3445,20 +3355,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>组件及支架</t>
+          <t>土建工程</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="E5" t="n">
-        <v>8000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -3466,20 +3376,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>逆变器及电气</t>
+          <t>设备采购</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>3000000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -3487,14 +3397,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>施工安装</t>
+          <t>安装调试</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>3000000</v>
+        <v>2500000</v>
       </c>
     </row>
   </sheetData>
@@ -3524,17 +3434,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>用能方</t>
+          <t>采购方</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>产权方</t>
+          <t>使用方</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>电费计算</t>
+          <t>定价方式</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -3551,27 +3461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>杭州钱塘光伏项目</t>
+          <t>A区精密加工中心</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>分布式光伏发电项目合同能源管理合同</t>
+          <t>精密零部件销售框架合同</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州钱塘制造有限公司</t>
+          <t>北方商贸集团有限公司</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>杭州钱塘产业园管理有限公司</t>
+          <t>北方商贸集团</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>自发自用电量按0.80元/kWh结算</t>
+          <t>市场价定价，季度调整</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3588,27 +3498,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>宁波北仑光伏项目</t>
+          <t>D区自动化装配线</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>宁波北仑光伏发电EMC合同</t>
+          <t>自动化配件加工合同</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>国网浙江省电力有限公司</t>
+          <t>西部工业材料有限公司</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>宁波北仑开发区管委会</t>
+          <t>西部工业材料</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>全额上网，按标杆电价0.4153元/kWh结算</t>
+          <t>固定单价，年度调整</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3618,7 +3528,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>按国家相关规定执行</t>
+          <t>按合同约定执行</t>
         </is>
       </c>
     </row>

--- a/data/demo_data.xlsx
+++ b/data/demo_data.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,6 +538,34 @@
       </c>
       <c r="B9" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>特殊事项</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>公司简介</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>东海精密制造有限公司成立于2020年，注册资本5000万元。
+公司主营精密机械零部件制造及自动化设备研发生产。
+目前拥有两个生产基地，产品覆盖华东、华南市场。</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1351,7 +1379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1444,6 +1472,18 @@
       </c>
       <c r="B9" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>企业类型</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>高新</t>
+        </is>
       </c>
     </row>
   </sheetData>
